--- a/mes-plugins/mes-plugins-master-orders/src/main/resources/masterOrders/public/resources/masterOrderImportSchema_pl.xlsx
+++ b/mes-plugins/mes-plugins-master-orders/src/main/resources/masterOrders/public/resources/masterOrderImportSchema_pl.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monikajedrysiak/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akazmierczak\Documents\Quantum Qguar\Qcadoo\Szablony\Import do Qcadoo\propozycje\PL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCA7913C-F755-434F-A65A-69E78DBC668F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="7880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="33600" windowHeight="7875" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Pozycje zam. sprzedaży - import" sheetId="1" r:id="rId1"/>
@@ -25,13 +24,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Łukasz Poniewierski</author>
-    <author>Monika Jędrysiak</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -141,7 +139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -177,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -213,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -260,7 +258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -297,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -321,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -345,7 +343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -371,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -397,7 +395,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -434,7 +432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -460,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -482,71 +480,8 @@
             <family val="2"/>
             <charset val="238"/>
           </rPr>
-          <t xml:space="preserve">Dana opcjonalna. Podaj wartość zdefiniowaną w słowniku Zamówienia sprzedaży - status pozycji. Jeśli nie wypełnisz kolumny nadamy status Nowa.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{8F220F2C-C051-B44E-ABB6-16171ADB1BAA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">qcadoo MES:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">Dana opcjonalna. Wskaż umówioną datę dostawy zamówionego produktu.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{610A4888-FD8E-984E-9300-D415FE475119}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t>qcadoo MES:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t>Dana opcjonalna. Podaj umówioną cenę sprzedaży pozycji zamówienia. Wprowadzona wartość musi być nieujemną liczbą.</t>
+          <t xml:space="preserve">Dana opcjonalna. Podaj wartość zdefiniowaną w słowniku Zlecenie nadrzędne - status pozycji. Jeśli nie wypełnisz kolumny nadamy status Nowa.
+</t>
         </r>
       </text>
     </comment>
@@ -555,7 +490,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Numer</t>
   </si>
@@ -598,18 +533,12 @@
   <si>
     <t>Status pozycji</t>
   </si>
-  <si>
-    <t>Data dostawy pozycji</t>
-  </si>
-  <si>
-    <t>Cena sprzedaży</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -660,12 +589,6 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -675,7 +598,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -683,24 +606,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -769,7 +684,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Styl tabeli 1" pivot="0" count="1" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Styl tabeli 1" pivot="0" count="1">
       <tableStyleElement type="wholeTable" dxfId="5"/>
     </tableStyle>
   </tableStyles>
@@ -804,7 +719,7 @@
         <xdr:cNvPr id="1050" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97A3254-EBA0-0A45-BB7C-63DAE4259A85}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97A3254-EBA0-0A45-BB7C-63DAE4259A85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -853,7 +768,7 @@
         <xdr:cNvPr id="1048" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3324B8BE-F0F9-D04D-B919-178894C1FEE4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3324B8BE-F0F9-D04D-B919-178894C1FEE4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -902,7 +817,7 @@
         <xdr:cNvPr id="1046" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72EB3432-E52C-E341-8116-3225AC86D3E5}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72EB3432-E52C-E341-8116-3225AC86D3E5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -951,7 +866,7 @@
         <xdr:cNvPr id="1044" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F131412A-160F-E64F-967F-F09418532A3C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F131412A-160F-E64F-967F-F09418532A3C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1000,7 +915,7 @@
         <xdr:cNvPr id="1042" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39FF3EAF-68FD-9346-813A-9FE8937BB301}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39FF3EAF-68FD-9346-813A-9FE8937BB301}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1049,7 +964,7 @@
         <xdr:cNvPr id="1040" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A9E0793-ECA4-F341-A219-451E356AFEAB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A9E0793-ECA4-F341-A219-451E356AFEAB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1098,7 +1013,7 @@
         <xdr:cNvPr id="1038" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61D3C515-0182-0C44-8CF1-5B09D4BC5EF0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61D3C515-0182-0C44-8CF1-5B09D4BC5EF0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1147,7 +1062,7 @@
         <xdr:cNvPr id="1036" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E7E608-94EB-4543-94BE-BF3E0B7910AB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E7E608-94EB-4543-94BE-BF3E0B7910AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1196,7 +1111,7 @@
         <xdr:cNvPr id="1034" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30786922-EB01-134F-BCB4-70E2DC99309B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30786922-EB01-134F-BCB4-70E2DC99309B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1245,7 +1160,7 @@
         <xdr:cNvPr id="1032" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15D1A257-F1D4-8E4B-A30F-ABA7BC329DA8}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15D1A257-F1D4-8E4B-A30F-ABA7BC329DA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1294,7 +1209,7 @@
         <xdr:cNvPr id="1030" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7485639-714A-4747-AD3E-5B7C923BB237}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7485639-714A-4747-AD3E-5B7C923BB237}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1343,7 +1258,7 @@
         <xdr:cNvPr id="1028" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02CC3FAB-C0BF-A747-A87B-8E61A4DE4DB2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02CC3FAB-C0BF-A747-A87B-8E61A4DE4DB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1392,7 +1307,7 @@
         <xdr:cNvPr id="1026" name="shapetype_202" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B7B3336-3A71-4546-86DD-F4C78B874A40}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B7B3336-3A71-4546-86DD-F4C78B874A40}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1426,30 +1341,24 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:P2" insertRow="1" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
-  <autoFilter ref="A1:P2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Numer" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Produkt" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ilość" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nazwa"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Opis"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Kontrahent"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data rozpoczęcia"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Data zakończenia"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Termin ostateczny"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Data wpływu"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Opis realizacji"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Technologia"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Uwagi"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Status pozycji"/>
-    <tableColumn id="17" xr3:uid="{D2D22E64-5E0E-224F-BD3A-A2C470778B1F}" name="Data dostawy pozycji"/>
-    <tableColumn id="18" xr3:uid="{9F9A64DB-7077-DC44-97B7-8B3D09DB5B51}" name="Cena sprzedaży"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:N2" insertRow="1" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3">
+  <autoFilter ref="A1:N2"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="Numer" dataDxfId="2"/>
+    <tableColumn id="2" name="Produkt" dataDxfId="1"/>
+    <tableColumn id="3" name="Ilość" dataDxfId="0"/>
+    <tableColumn id="4" name="Nazwa"/>
+    <tableColumn id="5" name="Opis"/>
+    <tableColumn id="6" name="Kontrahent"/>
+    <tableColumn id="7" name="Data rozpoczęcia"/>
+    <tableColumn id="8" name="Data zakończenia"/>
+    <tableColumn id="9" name="Termin ostateczny"/>
+    <tableColumn id="10" name="Data wpływu"/>
+    <tableColumn id="11" name="Opis realizacji"/>
+    <tableColumn id="12" name="Technologia"/>
+    <tableColumn id="13" name="Uwagi"/>
+    <tableColumn id="14" name="Status pozycji"/>
   </tableColumns>
   <tableStyleInfo name="Styl tabeli 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1751,19 +1660,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="16.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="7" max="11" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.875" customWidth="1"/>
+    <col min="7" max="11" width="20.875" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1800,23 +1709,28 @@
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
